--- a/docs/培训/OpenWorker培训/03-设备点检/点检表.xlsx
+++ b/docs/培训/OpenWorker培训/03-设备点检/点检表.xlsx
@@ -476,7 +476,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -530,7 +530,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46290</v>
+        <v>46296</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46290</v>
+        <v>46296</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46290</v>
+        <v>46296</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46290</v>
+        <v>46296</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46290</v>
+        <v>46296</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46290</v>
+        <v>46296</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46290</v>
+        <v>46296</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46264</v>
+        <v>46269</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46287</v>
+        <v>46292</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46282</v>
+        <v>46287</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46287</v>
+        <v>46292</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46284</v>
+        <v>46289</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
